--- a/out/서류/WISE_학교자율시간_진도표.xlsx
+++ b/out/서류/WISE_학교자율시간_진도표.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>데이터 수집·라벨링 활동지, 모델 테스트 기록</t>
+          <t>라벨 20장과 학급 비교, 정확도 기록(전체 · 데이터 축소), 사람과 AI의 역할 구분표, 배움 문장</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
@@ -612,7 +612,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>환각 사례 카드 2장 이상, 교차 검증 기록지</t>
+          <t>문항 5개 판정 기록, 검증 3단계 기록, 환각 사례 카드 2장, 배움 문장</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
